--- a/ejemplos/resultados/plan-del-grupo.xlsx
+++ b/ejemplos/resultados/plan-del-grupo.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asignaturas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan del grupo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Asignaturas">OFFSET(Asignaturas!$A$4,0,0,COUNTA(Asignaturas!$A$4:$A$29),5)</definedName>
+    <definedName name="Asignaturas">OFFSET('Plan del grupo'!$A$4,0,0,COUNTA('Plan del grupo'!$A$4:$A$29),5)</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,22 +494,24 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Asignaturas</t>
+          <t>Plan del grupo</t>
         </is>
       </c>
     </row>
@@ -539,6 +541,16 @@
           <t>Faltan</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>(nivel de las marcas)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -558,7 +570,15 @@
         <v>3</v>
       </c>
       <c r="E4" s="3">
-        <f>IF($A4="","",($C4-$D4))</f>
+        <f>IF(AND($A4=""),"",(IFERROR(VALUE($C4&amp;""),0)-IFERROR(VALUE($D4&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>IF(AND($A4=""),"",MID(IF((IFERROR(VALUE($D4&amp;""),0)&lt;IFERROR(VALUE($C4&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E4),IF($E4=0,"0",ROUND($E4,9-INT(LOG10(ABS($E4))))&amp;""),$E4&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E4&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D4&amp;""),0)&gt;IFERROR(VALUE($C4&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))),IF((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))))))&amp;""),(IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))),IF((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))))))&amp;""),(IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))),IF((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))))))&amp;""),(IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))),IF((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))))))&amp;""),(IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))),IF((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))))))&amp;""),(IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D4&amp;""),0)-IFERROR(VALUE($C4&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D4,$C4),NOT(($D4=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G4" s="3">
+        <f>IF(OR((IFERROR(VALUE($D4&amp;""),0)&gt;IFERROR(VALUE($C4&amp;""),0))),3,IF(OR((IFERROR(VALUE($D4&amp;""),0)&lt;IFERROR(VALUE($C4&amp;""),0))),2,IF(OR(AND(EXACT($D4,$C4),NOT(($D4="")))),1,0)))</f>
         <v/>
       </c>
     </row>
@@ -580,7 +600,15 @@
         <v>2</v>
       </c>
       <c r="E5" s="3">
-        <f>IF($A5="","",($C5-$D5))</f>
+        <f>IF(AND($A5=""),"",(IFERROR(VALUE($C5&amp;""),0)-IFERROR(VALUE($D5&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>IF(AND($A5=""),"",MID(IF((IFERROR(VALUE($D5&amp;""),0)&lt;IFERROR(VALUE($C5&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E5),IF($E5=0,"0",ROUND($E5,9-INT(LOG10(ABS($E5))))&amp;""),$E5&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E5&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D5&amp;""),0)&gt;IFERROR(VALUE($C5&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))),IF((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))))))&amp;""),(IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))),IF((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))))))&amp;""),(IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))),IF((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))))))&amp;""),(IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))),IF((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))))))&amp;""),(IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))),IF((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))))))&amp;""),(IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D5&amp;""),0)-IFERROR(VALUE($C5&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D5,$C5),NOT(($D5=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>IF(OR((IFERROR(VALUE($D5&amp;""),0)&gt;IFERROR(VALUE($C5&amp;""),0))),3,IF(OR((IFERROR(VALUE($D5&amp;""),0)&lt;IFERROR(VALUE($C5&amp;""),0))),2,IF(OR(AND(EXACT($D5,$C5),NOT(($D5="")))),1,0)))</f>
         <v/>
       </c>
     </row>
@@ -602,7 +630,15 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <f>IF($A6="","",($C6-$D6))</f>
+        <f>IF(AND($A6=""),"",(IFERROR(VALUE($C6&amp;""),0)-IFERROR(VALUE($D6&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>IF(AND($A6=""),"",MID(IF((IFERROR(VALUE($D6&amp;""),0)&lt;IFERROR(VALUE($C6&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E6),IF($E6=0,"0",ROUND($E6,9-INT(LOG10(ABS($E6))))&amp;""),$E6&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E6&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D6&amp;""),0)&gt;IFERROR(VALUE($C6&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))),IF((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))))))&amp;""),(IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))),IF((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))))))&amp;""),(IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))),IF((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))))))&amp;""),(IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))),IF((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))))))&amp;""),(IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))),IF((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))))))&amp;""),(IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D6&amp;""),0)-IFERROR(VALUE($C6&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D6,$C6),NOT(($D6=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G6" s="3">
+        <f>IF(OR((IFERROR(VALUE($D6&amp;""),0)&gt;IFERROR(VALUE($C6&amp;""),0))),3,IF(OR((IFERROR(VALUE($D6&amp;""),0)&lt;IFERROR(VALUE($C6&amp;""),0))),2,IF(OR(AND(EXACT($D6,$C6),NOT(($D6="")))),1,0)))</f>
         <v/>
       </c>
     </row>
@@ -624,7 +660,15 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <f>IF($A7="","",($C7-$D7))</f>
+        <f>IF(AND($A7=""),"",(IFERROR(VALUE($C7&amp;""),0)-IFERROR(VALUE($D7&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F7" s="3">
+        <f>IF(AND($A7=""),"",MID(IF((IFERROR(VALUE($D7&amp;""),0)&lt;IFERROR(VALUE($C7&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E7),IF($E7=0,"0",ROUND($E7,9-INT(LOG10(ABS($E7))))&amp;""),$E7&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E7&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D7&amp;""),0)&gt;IFERROR(VALUE($C7&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))),IF((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))))))&amp;""),(IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))),IF((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))))))&amp;""),(IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))),IF((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))))))&amp;""),(IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))),IF((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))))))&amp;""),(IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))),IF((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))))))&amp;""),(IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D7&amp;""),0)-IFERROR(VALUE($C7&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D7,$C7),NOT(($D7=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G7" s="3">
+        <f>IF(OR((IFERROR(VALUE($D7&amp;""),0)&gt;IFERROR(VALUE($C7&amp;""),0))),3,IF(OR((IFERROR(VALUE($D7&amp;""),0)&lt;IFERROR(VALUE($C7&amp;""),0))),2,IF(OR(AND(EXACT($D7,$C7),NOT(($D7="")))),1,0)))</f>
         <v/>
       </c>
     </row>
@@ -646,7 +690,15 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <f>IF($A8="","",($C8-$D8))</f>
+        <f>IF(AND($A8=""),"",(IFERROR(VALUE($C8&amp;""),0)-IFERROR(VALUE($D8&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>IF(AND($A8=""),"",MID(IF((IFERROR(VALUE($D8&amp;""),0)&lt;IFERROR(VALUE($C8&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E8),IF($E8=0,"0",ROUND($E8,9-INT(LOG10(ABS($E8))))&amp;""),$E8&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E8&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D8&amp;""),0)&gt;IFERROR(VALUE($C8&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))),IF((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))))))&amp;""),(IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))),IF((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))))))&amp;""),(IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))),IF((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))))))&amp;""),(IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))),IF((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))))))&amp;""),(IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))),IF((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))))))&amp;""),(IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D8&amp;""),0)-IFERROR(VALUE($C8&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D8,$C8),NOT(($D8=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G8" s="3">
+        <f>IF(OR((IFERROR(VALUE($D8&amp;""),0)&gt;IFERROR(VALUE($C8&amp;""),0))),3,IF(OR((IFERROR(VALUE($D8&amp;""),0)&lt;IFERROR(VALUE($C8&amp;""),0))),2,IF(OR(AND(EXACT($D8,$C8),NOT(($D8="")))),1,0)))</f>
         <v/>
       </c>
     </row>
@@ -668,207 +720,375 @@
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <f>IF($A9="","",($C9-$D9))</f>
+        <f>IF(AND($A9=""),"",(IFERROR(VALUE($C9&amp;""),0)-IFERROR(VALUE($D9&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>IF(AND($A9=""),"",MID(IF((IFERROR(VALUE($D9&amp;""),0)&lt;IFERROR(VALUE($C9&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E9),IF($E9=0,"0",ROUND($E9,9-INT(LOG10(ABS($E9))))&amp;""),$E9&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E9&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D9&amp;""),0)&gt;IFERROR(VALUE($C9&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))),IF((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))))))&amp;""),(IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))),IF((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))))))&amp;""),(IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))),IF((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))))))&amp;""),(IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))),IF((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))))))&amp;""),(IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))),IF((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))))))&amp;""),(IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D9&amp;""),0)-IFERROR(VALUE($C9&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D9,$C9),NOT(($D9=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G9" s="3">
+        <f>IF(OR((IFERROR(VALUE($D9&amp;""),0)&gt;IFERROR(VALUE($C9&amp;""),0))),3,IF(OR((IFERROR(VALUE($D9&amp;""),0)&lt;IFERROR(VALUE($C9&amp;""),0))),2,IF(OR(AND(EXACT($D9,$C9),NOT(($D9="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="3">
-        <f>IF($A10="","",($C10-$D10))</f>
+        <f>IF(AND($A10=""),"",(IFERROR(VALUE($C10&amp;""),0)-IFERROR(VALUE($D10&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>IF(AND($A10=""),"",MID(IF((IFERROR(VALUE($D10&amp;""),0)&lt;IFERROR(VALUE($C10&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E10),IF($E10=0,"0",ROUND($E10,9-INT(LOG10(ABS($E10))))&amp;""),$E10&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E10&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D10&amp;""),0)&gt;IFERROR(VALUE($C10&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))),IF((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))))))&amp;""),(IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))),IF((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))))))&amp;""),(IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))),IF((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))))))&amp;""),(IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))),IF((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))))))&amp;""),(IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))),IF((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))))))&amp;""),(IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D10&amp;""),0)-IFERROR(VALUE($C10&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D10,$C10),NOT(($D10=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G10" s="3">
+        <f>IF(OR((IFERROR(VALUE($D10&amp;""),0)&gt;IFERROR(VALUE($C10&amp;""),0))),3,IF(OR((IFERROR(VALUE($D10&amp;""),0)&lt;IFERROR(VALUE($C10&amp;""),0))),2,IF(OR(AND(EXACT($D10,$C10),NOT(($D10="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="3">
-        <f>IF($A11="","",($C11-$D11))</f>
+        <f>IF(AND($A11=""),"",(IFERROR(VALUE($C11&amp;""),0)-IFERROR(VALUE($D11&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>IF(AND($A11=""),"",MID(IF((IFERROR(VALUE($D11&amp;""),0)&lt;IFERROR(VALUE($C11&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E11),IF($E11=0,"0",ROUND($E11,9-INT(LOG10(ABS($E11))))&amp;""),$E11&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E11&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D11&amp;""),0)&gt;IFERROR(VALUE($C11&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))),IF((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))))))&amp;""),(IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))),IF((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))))))&amp;""),(IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))),IF((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))))))&amp;""),(IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))),IF((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))))))&amp;""),(IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))),IF((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))))))&amp;""),(IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D11&amp;""),0)-IFERROR(VALUE($C11&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D11,$C11),NOT(($D11=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G11" s="3">
+        <f>IF(OR((IFERROR(VALUE($D11&amp;""),0)&gt;IFERROR(VALUE($C11&amp;""),0))),3,IF(OR((IFERROR(VALUE($D11&amp;""),0)&lt;IFERROR(VALUE($C11&amp;""),0))),2,IF(OR(AND(EXACT($D11,$C11),NOT(($D11="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="3">
-        <f>IF($A12="","",($C12-$D12))</f>
+        <f>IF(AND($A12=""),"",(IFERROR(VALUE($C12&amp;""),0)-IFERROR(VALUE($D12&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="3">
+        <f>IF(AND($A12=""),"",MID(IF((IFERROR(VALUE($D12&amp;""),0)&lt;IFERROR(VALUE($C12&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E12),IF($E12=0,"0",ROUND($E12,9-INT(LOG10(ABS($E12))))&amp;""),$E12&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E12&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D12&amp;""),0)&gt;IFERROR(VALUE($C12&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))),IF((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))))))&amp;""),(IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))),IF((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))))))&amp;""),(IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))),IF((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))))))&amp;""),(IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))),IF((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))))))&amp;""),(IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))),IF((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))))))&amp;""),(IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D12&amp;""),0)-IFERROR(VALUE($C12&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D12,$C12),NOT(($D12=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G12" s="3">
+        <f>IF(OR((IFERROR(VALUE($D12&amp;""),0)&gt;IFERROR(VALUE($C12&amp;""),0))),3,IF(OR((IFERROR(VALUE($D12&amp;""),0)&lt;IFERROR(VALUE($C12&amp;""),0))),2,IF(OR(AND(EXACT($D12,$C12),NOT(($D12="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="3">
-        <f>IF($A13="","",($C13-$D13))</f>
+        <f>IF(AND($A13=""),"",(IFERROR(VALUE($C13&amp;""),0)-IFERROR(VALUE($D13&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>IF(AND($A13=""),"",MID(IF((IFERROR(VALUE($D13&amp;""),0)&lt;IFERROR(VALUE($C13&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E13),IF($E13=0,"0",ROUND($E13,9-INT(LOG10(ABS($E13))))&amp;""),$E13&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E13&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D13&amp;""),0)&gt;IFERROR(VALUE($C13&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))),IF((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))))))&amp;""),(IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))),IF((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))))))&amp;""),(IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))),IF((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))))))&amp;""),(IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))),IF((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))))))&amp;""),(IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))),IF((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))))))&amp;""),(IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D13&amp;""),0)-IFERROR(VALUE($C13&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D13,$C13),NOT(($D13=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G13" s="3">
+        <f>IF(OR((IFERROR(VALUE($D13&amp;""),0)&gt;IFERROR(VALUE($C13&amp;""),0))),3,IF(OR((IFERROR(VALUE($D13&amp;""),0)&lt;IFERROR(VALUE($C13&amp;""),0))),2,IF(OR(AND(EXACT($D13,$C13),NOT(($D13="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="3">
-        <f>IF($A14="","",($C14-$D14))</f>
+        <f>IF(AND($A14=""),"",(IFERROR(VALUE($C14&amp;""),0)-IFERROR(VALUE($D14&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
+        <f>IF(AND($A14=""),"",MID(IF((IFERROR(VALUE($D14&amp;""),0)&lt;IFERROR(VALUE($C14&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E14),IF($E14=0,"0",ROUND($E14,9-INT(LOG10(ABS($E14))))&amp;""),$E14&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E14&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D14&amp;""),0)&gt;IFERROR(VALUE($C14&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))),IF((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))))))&amp;""),(IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))),IF((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))))))&amp;""),(IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))),IF((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))))))&amp;""),(IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))),IF((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))))))&amp;""),(IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))),IF((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))))))&amp;""),(IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D14&amp;""),0)-IFERROR(VALUE($C14&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D14,$C14),NOT(($D14=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G14" s="3">
+        <f>IF(OR((IFERROR(VALUE($D14&amp;""),0)&gt;IFERROR(VALUE($C14&amp;""),0))),3,IF(OR((IFERROR(VALUE($D14&amp;""),0)&lt;IFERROR(VALUE($C14&amp;""),0))),2,IF(OR(AND(EXACT($D14,$C14),NOT(($D14="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="3">
-        <f>IF($A15="","",($C15-$D15))</f>
+        <f>IF(AND($A15=""),"",(IFERROR(VALUE($C15&amp;""),0)-IFERROR(VALUE($D15&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>IF(AND($A15=""),"",MID(IF((IFERROR(VALUE($D15&amp;""),0)&lt;IFERROR(VALUE($C15&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E15),IF($E15=0,"0",ROUND($E15,9-INT(LOG10(ABS($E15))))&amp;""),$E15&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E15&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D15&amp;""),0)&gt;IFERROR(VALUE($C15&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))),IF((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))))))&amp;""),(IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))),IF((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))))))&amp;""),(IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))),IF((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))))))&amp;""),(IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))),IF((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))))))&amp;""),(IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))),IF((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))))))&amp;""),(IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D15&amp;""),0)-IFERROR(VALUE($C15&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D15,$C15),NOT(($D15=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G15" s="3">
+        <f>IF(OR((IFERROR(VALUE($D15&amp;""),0)&gt;IFERROR(VALUE($C15&amp;""),0))),3,IF(OR((IFERROR(VALUE($D15&amp;""),0)&lt;IFERROR(VALUE($C15&amp;""),0))),2,IF(OR(AND(EXACT($D15,$C15),NOT(($D15="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="3">
-        <f>IF($A16="","",($C16-$D16))</f>
+        <f>IF(AND($A16=""),"",(IFERROR(VALUE($C16&amp;""),0)-IFERROR(VALUE($D16&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F16" s="3">
+        <f>IF(AND($A16=""),"",MID(IF((IFERROR(VALUE($D16&amp;""),0)&lt;IFERROR(VALUE($C16&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E16),IF($E16=0,"0",ROUND($E16,9-INT(LOG10(ABS($E16))))&amp;""),$E16&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E16&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D16&amp;""),0)&gt;IFERROR(VALUE($C16&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))),IF((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))))))&amp;""),(IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))),IF((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))))))&amp;""),(IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))),IF((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))))))&amp;""),(IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))),IF((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))))))&amp;""),(IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))),IF((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))))))&amp;""),(IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D16&amp;""),0)-IFERROR(VALUE($C16&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D16,$C16),NOT(($D16=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G16" s="3">
+        <f>IF(OR((IFERROR(VALUE($D16&amp;""),0)&gt;IFERROR(VALUE($C16&amp;""),0))),3,IF(OR((IFERROR(VALUE($D16&amp;""),0)&lt;IFERROR(VALUE($C16&amp;""),0))),2,IF(OR(AND(EXACT($D16,$C16),NOT(($D16="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="3">
-        <f>IF($A17="","",($C17-$D17))</f>
+        <f>IF(AND($A17=""),"",(IFERROR(VALUE($C17&amp;""),0)-IFERROR(VALUE($D17&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F17" s="3">
+        <f>IF(AND($A17=""),"",MID(IF((IFERROR(VALUE($D17&amp;""),0)&lt;IFERROR(VALUE($C17&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E17),IF($E17=0,"0",ROUND($E17,9-INT(LOG10(ABS($E17))))&amp;""),$E17&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E17&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D17&amp;""),0)&gt;IFERROR(VALUE($C17&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))),IF((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))))))&amp;""),(IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))),IF((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))))))&amp;""),(IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))),IF((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))))))&amp;""),(IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))),IF((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))))))&amp;""),(IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))),IF((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))))))&amp;""),(IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D17&amp;""),0)-IFERROR(VALUE($C17&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D17,$C17),NOT(($D17=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G17" s="3">
+        <f>IF(OR((IFERROR(VALUE($D17&amp;""),0)&gt;IFERROR(VALUE($C17&amp;""),0))),3,IF(OR((IFERROR(VALUE($D17&amp;""),0)&lt;IFERROR(VALUE($C17&amp;""),0))),2,IF(OR(AND(EXACT($D17,$C17),NOT(($D17="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="3">
-        <f>IF($A18="","",($C18-$D18))</f>
+        <f>IF(AND($A18=""),"",(IFERROR(VALUE($C18&amp;""),0)-IFERROR(VALUE($D18&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F18" s="3">
+        <f>IF(AND($A18=""),"",MID(IF((IFERROR(VALUE($D18&amp;""),0)&lt;IFERROR(VALUE($C18&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E18),IF($E18=0,"0",ROUND($E18,9-INT(LOG10(ABS($E18))))&amp;""),$E18&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E18&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D18&amp;""),0)&gt;IFERROR(VALUE($C18&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))),IF((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))))))&amp;""),(IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))),IF((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))))))&amp;""),(IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))),IF((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))))))&amp;""),(IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))),IF((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))))))&amp;""),(IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))),IF((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))))))&amp;""),(IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D18&amp;""),0)-IFERROR(VALUE($C18&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D18,$C18),NOT(($D18=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G18" s="3">
+        <f>IF(OR((IFERROR(VALUE($D18&amp;""),0)&gt;IFERROR(VALUE($C18&amp;""),0))),3,IF(OR((IFERROR(VALUE($D18&amp;""),0)&lt;IFERROR(VALUE($C18&amp;""),0))),2,IF(OR(AND(EXACT($D18,$C18),NOT(($D18="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="3">
-        <f>IF($A19="","",($C19-$D19))</f>
+        <f>IF(AND($A19=""),"",(IFERROR(VALUE($C19&amp;""),0)-IFERROR(VALUE($D19&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="3">
+        <f>IF(AND($A19=""),"",MID(IF((IFERROR(VALUE($D19&amp;""),0)&lt;IFERROR(VALUE($C19&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E19),IF($E19=0,"0",ROUND($E19,9-INT(LOG10(ABS($E19))))&amp;""),$E19&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E19&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D19&amp;""),0)&gt;IFERROR(VALUE($C19&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))),IF((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))))))&amp;""),(IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))),IF((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))))))&amp;""),(IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))),IF((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))))))&amp;""),(IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))),IF((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))))))&amp;""),(IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))),IF((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))))))&amp;""),(IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D19&amp;""),0)-IFERROR(VALUE($C19&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D19,$C19),NOT(($D19=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G19" s="3">
+        <f>IF(OR((IFERROR(VALUE($D19&amp;""),0)&gt;IFERROR(VALUE($C19&amp;""),0))),3,IF(OR((IFERROR(VALUE($D19&amp;""),0)&lt;IFERROR(VALUE($C19&amp;""),0))),2,IF(OR(AND(EXACT($D19,$C19),NOT(($D19="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="3">
-        <f>IF($A20="","",($C20-$D20))</f>
+        <f>IF(AND($A20=""),"",(IFERROR(VALUE($C20&amp;""),0)-IFERROR(VALUE($D20&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F20" s="3">
+        <f>IF(AND($A20=""),"",MID(IF((IFERROR(VALUE($D20&amp;""),0)&lt;IFERROR(VALUE($C20&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E20),IF($E20=0,"0",ROUND($E20,9-INT(LOG10(ABS($E20))))&amp;""),$E20&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E20&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D20&amp;""),0)&gt;IFERROR(VALUE($C20&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))),IF((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))))))&amp;""),(IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))),IF((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))))))&amp;""),(IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))),IF((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))))))&amp;""),(IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))),IF((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))))))&amp;""),(IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))),IF((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))))))&amp;""),(IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D20&amp;""),0)-IFERROR(VALUE($C20&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D20,$C20),NOT(($D20=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G20" s="3">
+        <f>IF(OR((IFERROR(VALUE($D20&amp;""),0)&gt;IFERROR(VALUE($C20&amp;""),0))),3,IF(OR((IFERROR(VALUE($D20&amp;""),0)&lt;IFERROR(VALUE($C20&amp;""),0))),2,IF(OR(AND(EXACT($D20,$C20),NOT(($D20="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="3">
-        <f>IF($A21="","",($C21-$D21))</f>
+        <f>IF(AND($A21=""),"",(IFERROR(VALUE($C21&amp;""),0)-IFERROR(VALUE($D21&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>IF(AND($A21=""),"",MID(IF((IFERROR(VALUE($D21&amp;""),0)&lt;IFERROR(VALUE($C21&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E21),IF($E21=0,"0",ROUND($E21,9-INT(LOG10(ABS($E21))))&amp;""),$E21&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E21&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D21&amp;""),0)&gt;IFERROR(VALUE($C21&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))),IF((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))))))&amp;""),(IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))),IF((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))))))&amp;""),(IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))),IF((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))))))&amp;""),(IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))),IF((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))))))&amp;""),(IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))),IF((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))))))&amp;""),(IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D21&amp;""),0)-IFERROR(VALUE($C21&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D21,$C21),NOT(($D21=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G21" s="3">
+        <f>IF(OR((IFERROR(VALUE($D21&amp;""),0)&gt;IFERROR(VALUE($C21&amp;""),0))),3,IF(OR((IFERROR(VALUE($D21&amp;""),0)&lt;IFERROR(VALUE($C21&amp;""),0))),2,IF(OR(AND(EXACT($D21,$C21),NOT(($D21="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="3">
-        <f>IF($A22="","",($C22-$D22))</f>
+        <f>IF(AND($A22=""),"",(IFERROR(VALUE($C22&amp;""),0)-IFERROR(VALUE($D22&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="3">
+        <f>IF(AND($A22=""),"",MID(IF((IFERROR(VALUE($D22&amp;""),0)&lt;IFERROR(VALUE($C22&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E22),IF($E22=0,"0",ROUND($E22,9-INT(LOG10(ABS($E22))))&amp;""),$E22&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E22&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D22&amp;""),0)&gt;IFERROR(VALUE($C22&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))),IF((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))))))&amp;""),(IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))),IF((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))))))&amp;""),(IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))),IF((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))))))&amp;""),(IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))),IF((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))))))&amp;""),(IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))),IF((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))))))&amp;""),(IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D22&amp;""),0)-IFERROR(VALUE($C22&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D22,$C22),NOT(($D22=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G22" s="3">
+        <f>IF(OR((IFERROR(VALUE($D22&amp;""),0)&gt;IFERROR(VALUE($C22&amp;""),0))),3,IF(OR((IFERROR(VALUE($D22&amp;""),0)&lt;IFERROR(VALUE($C22&amp;""),0))),2,IF(OR(AND(EXACT($D22,$C22),NOT(($D22="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="3">
-        <f>IF($A23="","",($C23-$D23))</f>
+        <f>IF(AND($A23=""),"",(IFERROR(VALUE($C23&amp;""),0)-IFERROR(VALUE($D23&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>IF(AND($A23=""),"",MID(IF((IFERROR(VALUE($D23&amp;""),0)&lt;IFERROR(VALUE($C23&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E23),IF($E23=0,"0",ROUND($E23,9-INT(LOG10(ABS($E23))))&amp;""),$E23&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E23&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D23&amp;""),0)&gt;IFERROR(VALUE($C23&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))),IF((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))))))&amp;""),(IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))),IF((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))))))&amp;""),(IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))),IF((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))))))&amp;""),(IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))),IF((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))))))&amp;""),(IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))),IF((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))))))&amp;""),(IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D23&amp;""),0)-IFERROR(VALUE($C23&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D23,$C23),NOT(($D23=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G23" s="3">
+        <f>IF(OR((IFERROR(VALUE($D23&amp;""),0)&gt;IFERROR(VALUE($C23&amp;""),0))),3,IF(OR((IFERROR(VALUE($D23&amp;""),0)&lt;IFERROR(VALUE($C23&amp;""),0))),2,IF(OR(AND(EXACT($D23,$C23),NOT(($D23="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="3">
-        <f>IF($A24="","",($C24-$D24))</f>
+        <f>IF(AND($A24=""),"",(IFERROR(VALUE($C24&amp;""),0)-IFERROR(VALUE($D24&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="3">
+        <f>IF(AND($A24=""),"",MID(IF((IFERROR(VALUE($D24&amp;""),0)&lt;IFERROR(VALUE($C24&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E24),IF($E24=0,"0",ROUND($E24,9-INT(LOG10(ABS($E24))))&amp;""),$E24&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E24&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D24&amp;""),0)&gt;IFERROR(VALUE($C24&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))),IF((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))))))&amp;""),(IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))),IF((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))))))&amp;""),(IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))),IF((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))))))&amp;""),(IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))),IF((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))))))&amp;""),(IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))),IF((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))))))&amp;""),(IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D24&amp;""),0)-IFERROR(VALUE($C24&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D24,$C24),NOT(($D24=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G24" s="3">
+        <f>IF(OR((IFERROR(VALUE($D24&amp;""),0)&gt;IFERROR(VALUE($C24&amp;""),0))),3,IF(OR((IFERROR(VALUE($D24&amp;""),0)&lt;IFERROR(VALUE($C24&amp;""),0))),2,IF(OR(AND(EXACT($D24,$C24),NOT(($D24="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="3">
-        <f>IF($A25="","",($C25-$D25))</f>
+        <f>IF(AND($A25=""),"",(IFERROR(VALUE($C25&amp;""),0)-IFERROR(VALUE($D25&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="3">
+        <f>IF(AND($A25=""),"",MID(IF((IFERROR(VALUE($D25&amp;""),0)&lt;IFERROR(VALUE($C25&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E25),IF($E25=0,"0",ROUND($E25,9-INT(LOG10(ABS($E25))))&amp;""),$E25&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E25&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D25&amp;""),0)&gt;IFERROR(VALUE($C25&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))),IF((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))))))&amp;""),(IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))),IF((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))))))&amp;""),(IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))),IF((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))))))&amp;""),(IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))),IF((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))))))&amp;""),(IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))),IF((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))))))&amp;""),(IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D25&amp;""),0)-IFERROR(VALUE($C25&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D25,$C25),NOT(($D25=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G25" s="3">
+        <f>IF(OR((IFERROR(VALUE($D25&amp;""),0)&gt;IFERROR(VALUE($C25&amp;""),0))),3,IF(OR((IFERROR(VALUE($D25&amp;""),0)&lt;IFERROR(VALUE($C25&amp;""),0))),2,IF(OR(AND(EXACT($D25,$C25),NOT(($D25="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="3">
-        <f>IF($A26="","",($C26-$D26))</f>
+        <f>IF(AND($A26=""),"",(IFERROR(VALUE($C26&amp;""),0)-IFERROR(VALUE($D26&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="3">
+        <f>IF(AND($A26=""),"",MID(IF((IFERROR(VALUE($D26&amp;""),0)&lt;IFERROR(VALUE($C26&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E26),IF($E26=0,"0",ROUND($E26,9-INT(LOG10(ABS($E26))))&amp;""),$E26&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E26&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D26&amp;""),0)&gt;IFERROR(VALUE($C26&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))),IF((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))))))&amp;""),(IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))),IF((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))))))&amp;""),(IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))),IF((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))))))&amp;""),(IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))),IF((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))))))&amp;""),(IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))),IF((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))))))&amp;""),(IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D26&amp;""),0)-IFERROR(VALUE($C26&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D26,$C26),NOT(($D26=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G26" s="3">
+        <f>IF(OR((IFERROR(VALUE($D26&amp;""),0)&gt;IFERROR(VALUE($C26&amp;""),0))),3,IF(OR((IFERROR(VALUE($D26&amp;""),0)&lt;IFERROR(VALUE($C26&amp;""),0))),2,IF(OR(AND(EXACT($D26,$C26),NOT(($D26="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="3">
-        <f>IF($A27="","",($C27-$D27))</f>
+        <f>IF(AND($A27=""),"",(IFERROR(VALUE($C27&amp;""),0)-IFERROR(VALUE($D27&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="3">
+        <f>IF(AND($A27=""),"",MID(IF((IFERROR(VALUE($D27&amp;""),0)&lt;IFERROR(VALUE($C27&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E27),IF($E27=0,"0",ROUND($E27,9-INT(LOG10(ABS($E27))))&amp;""),$E27&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E27&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D27&amp;""),0)&gt;IFERROR(VALUE($C27&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))),IF((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))))))&amp;""),(IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))),IF((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))))))&amp;""),(IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))),IF((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))))))&amp;""),(IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))),IF((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))))))&amp;""),(IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))),IF((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))))))&amp;""),(IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D27&amp;""),0)-IFERROR(VALUE($C27&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D27,$C27),NOT(($D27=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G27" s="3">
+        <f>IF(OR((IFERROR(VALUE($D27&amp;""),0)&gt;IFERROR(VALUE($C27&amp;""),0))),3,IF(OR((IFERROR(VALUE($D27&amp;""),0)&lt;IFERROR(VALUE($C27&amp;""),0))),2,IF(OR(AND(EXACT($D27,$C27),NOT(($D27="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="3">
-        <f>IF($A28="","",($C28-$D28))</f>
+        <f>IF(AND($A28=""),"",(IFERROR(VALUE($C28&amp;""),0)-IFERROR(VALUE($D28&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>IF(AND($A28=""),"",MID(IF((IFERROR(VALUE($D28&amp;""),0)&lt;IFERROR(VALUE($C28&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E28),IF($E28=0,"0",ROUND($E28,9-INT(LOG10(ABS($E28))))&amp;""),$E28&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E28&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D28&amp;""),0)&gt;IFERROR(VALUE($C28&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))),IF((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))))))&amp;""),(IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))),IF((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))))))&amp;""),(IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))),IF((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))))))&amp;""),(IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))),IF((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))))))&amp;""),(IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))),IF((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))))))&amp;""),(IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D28&amp;""),0)-IFERROR(VALUE($C28&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D28,$C28),NOT(($D28=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G28" s="3">
+        <f>IF(OR((IFERROR(VALUE($D28&amp;""),0)&gt;IFERROR(VALUE($C28&amp;""),0))),3,IF(OR((IFERROR(VALUE($D28&amp;""),0)&lt;IFERROR(VALUE($C28&amp;""),0))),2,IF(OR(AND(EXACT($D28,$C28),NOT(($D28="")))),1,0)))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="3">
-        <f>IF($A29="","",($C29-$D29))</f>
+        <f>IF(AND($A29=""),"",(IFERROR(VALUE($C29&amp;""),0)-IFERROR(VALUE($D29&amp;""),0)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>IF(AND($A29=""),"",MID(IF((IFERROR(VALUE($D29&amp;""),0)&lt;IFERROR(VALUE($C29&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"Falta","Faltan")&amp;"")&amp;" "&amp;IF(ISNUMBER($E29),IF($E29=0,"0",ROUND($E29,9-INT(LOG10(ABS($E29))))&amp;""),$E29&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE($E29&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF((IFERROR(VALUE($D29&amp;""),0)&gt;IFERROR(VALUE($C29&amp;""),0)),"; "&amp;IF(ISNUMBER((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))),IF((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))))))&amp;""),(IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))),IF((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))),IF((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))))))&amp;""),(IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))=0,"0",ROUND((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))),IF((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))))))&amp;""),(IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;"")),9-INT(LOG10(ABS((IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))),IF((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))))))&amp;""),(IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))))))&amp;""),(IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"Sobra","Sobran")&amp;"")&amp;" "&amp;IF(ISNUMBER((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))),IF((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))=0,"0",ROUND((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0)),9-INT(LOG10(ABS((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))))))&amp;""),(IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;"")&amp;" "&amp;IF(ISNUMBER(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")),IF(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")=0,"0",ROUND(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos"),9-INT(LOG10(ABS(IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")))))&amp;""),IF(IFERROR(VALUE((IFERROR(VALUE($D29&amp;""),0)-IFERROR(VALUE($C29&amp;""),0))&amp;""),0)=1,"turno","turnos")&amp;""))&amp;""),"")&amp;IF(AND(EXACT($D29,$C29),NOT(($D29=""))),"; "&amp;"completa",""),3,32767))</f>
+        <v/>
+      </c>
+      <c r="G29" s="3">
+        <f>IF(OR((IFERROR(VALUE($D29&amp;""),0)&gt;IFERROR(VALUE($C29&amp;""),0))),3,IF(OR((IFERROR(VALUE($D29&amp;""),0)&lt;IFERROR(VALUE($C29&amp;""),0))),2,IF(OR(AND(EXACT($D29,$C29),NOT(($D29="")))),1,0)))</f>
         <v/>
       </c>
     </row>
@@ -907,31 +1127,32 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <conditionalFormatting sqref="B4:B29">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>($D4&lt;$C4)</formula>
+      <formula>(IFERROR(VALUE($D4&amp;""),0)&lt;IFERROR(VALUE($C4&amp;""),0))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="0">
-      <formula>($D4&gt;$C4)</formula>
+      <formula>(IFERROR(VALUE($D4&amp;""),0)&gt;IFERROR(VALUE($C4&amp;""),0))</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="2" stopIfTrue="0">
-      <formula>AND(($D4=$C4),NOT(($D4="")))</formula>
+      <formula>AND(EXACT($D4,$C4),NOT(($D4="")))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D29">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>($D4&lt;$C4)</formula>
+      <formula>(IFERROR(VALUE($D4&amp;""),0)&lt;IFERROR(VALUE($C4&amp;""),0))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="0">
-      <formula>($D4&gt;$C4)</formula>
+      <formula>(IFERROR(VALUE($D4&amp;""),0)&gt;IFERROR(VALUE($C4&amp;""),0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E29">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>($D4&lt;$C4)</formula>
+      <formula>(IFERROR(VALUE($D4&amp;""),0)&lt;IFERROR(VALUE($C4&amp;""),0))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="1" stopIfTrue="0">
-      <formula>($D4&gt;$C4)</formula>
+      <formula>(IFERROR(VALUE($D4&amp;""),0)&gt;IFERROR(VALUE($C4&amp;""),0))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/ejemplos/resultados/plan-del-grupo.xlsx
+++ b/ejemplos/resultados/plan-del-grupo.xlsx
@@ -1103,7 +1103,7 @@
       <c r="A32" s="6" t="n"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>insuficiente</t>
+          <t>La asignatura tiene menos turnos asignados que su frecuencia</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       <c r="A33" s="7" t="n"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>excedida</t>
+          <t>La asignatura tiene mas turnos asignados que su frecuencia</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       <c r="A34" s="8" t="n"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>completa</t>
+          <t>La asignatura tiene todos sus turnos asignados</t>
         </is>
       </c>
     </row>
